--- a/results/summary_results.xlsx
+++ b/results/summary_results.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KPIs Multimodal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,61 +413,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>traffic_condition</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>avg_time</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>total_distance</t>
+          <t>avg_time_min</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>CO2_emissions</t>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_distance_km</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_cost_vnd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_cost_vnd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>total_co2_kg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>avg_co2_kg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>delivery_count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Full Multimodal</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>5.65780853013221</v>
-      </c>
       <c r="C2" t="n">
-        <v>497.8871506516344</v>
+        <v>3.11</v>
       </c>
       <c r="D2" t="n">
-        <v>59.74645807819613</v>
+        <v>272.08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F2" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J2" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Road + Metro</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>272.08</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F3" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H3" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J3" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>272.08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F4" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Off-Peak</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Road Only</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>5.65780853013221</v>
-      </c>
-      <c r="C3" t="n">
-        <v>497.8871506516344</v>
-      </c>
-      <c r="D3" t="n">
-        <v>59.74645807819613</v>
+      <c r="C5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>272.08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H5" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Full Multimodal</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="D6" t="n">
+        <v>272.08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J6" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Road + Metro</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="D7" t="n">
+        <v>272.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J7" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Road + Waterbus</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="D8" t="n">
+        <v>272.08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H8" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J8" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Road Only</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>272.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F9" t="n">
+        <v>816253.66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4664.31</v>
+      </c>
+      <c r="H9" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J9" t="n">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
